--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEVADA_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/NEVADA_2018.xlsx
@@ -2227,7 +2227,7 @@
         <v>15</v>
       </c>
       <c r="D104">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="105">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C123">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C171">
@@ -3631,7 +3631,7 @@
         <v>15</v>
       </c>
       <c r="D182">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="183">
@@ -3883,7 +3883,7 @@
         <v>15</v>
       </c>
       <c r="D196">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="197">
@@ -4495,7 +4495,7 @@
         <v>15</v>
       </c>
       <c r="D230">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="231">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C288">
@@ -6421,7 +6421,7 @@
         <v>15</v>
       </c>
       <c r="D337">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="338">
@@ -8707,7 +8707,7 @@
         <v>15</v>
       </c>
       <c r="D464">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="465">
@@ -8869,7 +8869,7 @@
         <v>15</v>
       </c>
       <c r="D473">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="474">
@@ -11533,7 +11533,7 @@
         <v>15</v>
       </c>
       <c r="D621">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="622">
@@ -12757,7 +12757,7 @@
         <v>15</v>
       </c>
       <c r="D689">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="690">
@@ -12829,7 +12829,7 @@
         <v>15</v>
       </c>
       <c r="D693">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="694">
@@ -13513,7 +13513,7 @@
         <v>15</v>
       </c>
       <c r="D731">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="732">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C786">
@@ -14964,7 +14964,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C812">
@@ -16681,7 +16681,7 @@
         <v>15</v>
       </c>
       <c r="D907">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="908">
@@ -19957,7 +19957,7 @@
         <v>15</v>
       </c>
       <c r="D1089">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="1090">
@@ -20137,7 +20137,7 @@
         <v>15</v>
       </c>
       <c r="D1099">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="1100">
@@ -22603,7 +22603,7 @@
         <v>15</v>
       </c>
       <c r="D1236">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="1237">
@@ -23485,7 +23485,7 @@
         <v>15</v>
       </c>
       <c r="D1285">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="1286">
@@ -23845,7 +23845,7 @@
         <v>15</v>
       </c>
       <c r="D1305">
-        <v>0.0009566326530612245</v>
+        <v>0.0009566326530612244</v>
       </c>
     </row>
     <row r="1306">
